--- a/AtchisonRegime/Outputs/Aust/ASX300/df_TESTCONTOUR_rawData.xlsx
+++ b/AtchisonRegime/Outputs/Aust/ASX300/df_TESTCONTOUR_rawData.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD534"/>
+  <dimension ref="A1:AD535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51745,6 +51745,102 @@
       </c>
       <c r="AD534" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="n">
+        <v>533</v>
+      </c>
+      <c r="B535" s="2" t="n">
+        <v>45473</v>
+      </c>
+      <c r="C535" t="n">
+        <v>-0.930850647666511</v>
+      </c>
+      <c r="D535" t="n">
+        <v>0.1957318122965168</v>
+      </c>
+      <c r="E535" t="b">
+        <v>0</v>
+      </c>
+      <c r="F535" t="b">
+        <v>1</v>
+      </c>
+      <c r="G535" t="n">
+        <v>1.013477167514609</v>
+      </c>
+      <c r="H535" t="n">
+        <v>9980775.000000019</v>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="K535" t="n">
+        <v>1.013477167514609</v>
+      </c>
+      <c r="L535" t="n">
+        <v>0</v>
+      </c>
+      <c r="M535" t="n">
+        <v>0</v>
+      </c>
+      <c r="N535" t="n">
+        <v>0</v>
+      </c>
+      <c r="O535" t="n">
+        <v>1468.827817204701</v>
+      </c>
+      <c r="P535" t="n">
+        <v>275.4740587243287</v>
+      </c>
+      <c r="Q535" t="n">
+        <v>144.5879049730617</v>
+      </c>
+      <c r="R535" t="n">
+        <v>145.2785989199411</v>
+      </c>
+      <c r="S535" t="n">
+        <v>5</v>
+      </c>
+      <c r="T535" t="n">
+        <v>1.013477167514609</v>
+      </c>
+      <c r="U535" t="n">
+        <v>2.99639478692959</v>
+      </c>
+      <c r="V535" t="n">
+        <v>0</v>
+      </c>
+      <c r="W535" t="n">
+        <v>0</v>
+      </c>
+      <c r="X535" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y535" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z535" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA535" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB535" t="n">
+        <v>13.38800024239097</v>
+      </c>
+      <c r="AC535" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AD535" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -52028,13 +52124,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF792FE-77E0-44AC-84E8-AB8BA7EEC981}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{191C0F75-E8F6-4BBC-AB37-D87B7C8BAFFB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{430D2B3A-DB37-448C-B1F6-A0A89A9A046B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B4A4AA6-783A-4542-9AA8-E0FA94CEE924}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF7BD399-8BED-4F0E-950C-F5CE4BC22D13}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB4DC451-5012-4FE0-A106-6C96F4223935}"/>
 </file>